--- a/Paket_3_Matematika_TKA_SD.xlsx
+++ b/Paket_3_Matematika_TKA_SD.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paket 3 Matematika" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,27 +471,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Matematika 1: contoh soal numerasi sederhana.</t>
+          <t>Ibu membuat sirup manis untuk acara arisan. Ibu mencampur 2,5 liter air matang, 1 1/4 liter sirup melon, dan 0,75 liter air kelapa muda. Seluruh minuman tersebut dituangkan ke dalam gelas-gelas kecil berukuran 1/4 liter hingga habis. Berapa banyak gelas yang terisi penuh oleh minuman sirup tersebut?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  16 gelas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  18 gelas</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  19 gelas</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  20 gelas</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -502,7 +502,11 @@
       <c r="H2" t="n">
         <v>60</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,27 +516,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Matematika 2: contoh soal numerasi sederhana.</t>
+          <t>Pada siang hari, suhu udara di puncak Gunung Bromo adalah 14°C. Menjelang tengah malam, suhu turun drastis sebesar 18°C. Berapakah suhu udara di puncak Gunung Bromo pada tengah malam tersebut?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  -2°C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  -4°C</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  -6°C</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  4°C</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -543,7 +547,11 @@
       <c r="H3" t="n">
         <v>60</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,27 +561,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Matematika 3: contoh soal numerasi sederhana.</t>
+          <t>Perbandingan uang saku Danu dan Eko adalah 4 : 7. Jika selisih uang saku mereka berdua adalah Rp15.000, berapakah jumlah uang saku Danu dan Eko seluruhnya?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Rp45.000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Rp55.000</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Rp60.000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Rp65.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -584,7 +592,11 @@
       <c r="H4" t="n">
         <v>60</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -594,27 +606,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Matematika 4: contoh soal numerasi sederhana.</t>
+          <t>Sebuah bak penampungan air berbentuk kubus memiliki volume 1.728 liter. Panjang rusuk bagian dalam bak penampungan air tersebut adalah....</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  100 cm</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  110 cm</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  120 cm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  140 cm</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -625,37 +637,42 @@
       <c r="H5" t="n">
         <v>60</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Matematika 5: contoh soal numerasi sederhana.</t>
+          <t>Dina menyiapkan paket bingkisan ulang tahun yang terdiri atas 40 gantungan kunci, 60 stiker kartun, dan 80 permen susu. Setiap kantong bingkisan diisi ketiga jenis barang tersebut dengan jumlah yang sama rata.
+Manakah pernyataan berikut yang BENAR?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Jumlah paket bingkisan paling banyak yang bisa dibuat Dina adalah 20 paket.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Setiap paket bingkisan berisi 2 buah gantungan kunci.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Setiap paket bingkisan berisi 4 buah stiker kartun.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Setiap paket bingkisan berisi 4 buah permen susu.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -666,7 +683,11 @@
       <c r="H6" t="n">
         <v>60</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -676,27 +697,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Matematika 6: contoh soal numerasi sederhana.</t>
+          <t>Hasil dari 450 + 350 : (-7) - 25 x 8 adalah....</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  200</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  250</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  300</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  350</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -707,17 +728,21 @@
       <c r="H7" t="n">
         <v>60</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Matematika 7: contoh soal numerasi sederhana.</t>
+          <t>Sebuah loyang pizza dipotong menjadi 12 bagian sama besar. Budi memakan 3 potong, Siti memakan 4 potong, dan sisanya dimakan Anton. Tentukan nilai kebenaran dari pernyataan berikut!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -748,7 +773,11 @@
       <c r="H8" t="n">
         <v>60</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -758,27 +787,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Matematika 8: contoh soal numerasi sederhana.</t>
+          <t>Rudi mendapat jadwal ronda malam setiap 6 hari sekali, sedangkan Pak Joko setiap 9 hari sekali. Jika pada hari Rabu, 10 Agustus mereka ronda malam bersama-sama, pada hari dan tanggal berapakah mereka akan bertugas bersama lagi untuk waktu terdekat berikutnya?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Minggu, 28 Agustus</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Senin, 29 Agustus</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Minggu, 27 Agustus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Senin, 28 Agustus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -789,7 +818,11 @@
       <c r="H9" t="n">
         <v>60</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -799,27 +832,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Matematika 9: contoh soal numerasi sederhana.</t>
+          <t>Denah sebuah ruang pertemuan digambar dengan skala 1 : 200. Pada denah, panjang ruangan adalah 8 cm dan lebarnya 5 cm. Luas sebenarnya dari ruang pertemuan tersebut adalah....</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  80 m²</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  160 m²</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  200 m²</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  240 m²</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -830,7 +863,11 @@
       <c r="H10" t="n">
         <v>60</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -840,27 +877,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Matematika 10: contoh soal numerasi sederhana.</t>
+          <t>Sebuah koperasi sekolah membeli 3 kodi buku tulis, 2 gros pulpen, dan 5 lusin pensil. Berapakah jumlah keseluruhan alat tulis yang dibeli koperasi tersebut dalam satuan buah?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  388 buah</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  408 buah</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  418 buah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  428 buah</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -871,7 +908,11 @@
       <c r="H11" t="n">
         <v>60</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -881,27 +922,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Matematika 11: contoh soal numerasi sederhana.</t>
+          <t>Sebuah bak mandi bervolume 360 liter diisi air menggunakan kran selama 20 menit hingga penuh. Berapakah debit aliran air kran tersebut dalam satuan liter/menit?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  16 liter/menit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  18 liter/menit</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  20 liter/menit</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  22 liter/menit</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -912,37 +953,41 @@
       <c r="H12" t="n">
         <v>60</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Matematika 12: contoh soal numerasi sederhana.</t>
+          <t>Perhatikan bangun datar segi empat belah ketupat. Manakah di antara sifat-sifat berikut yang BENAR mengenai belah ketupat?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Keempat sisinya memiliki panjang yang sama.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Kedua diagonalnya berpotongan tegak lurus dan saling membagi dua sama panjang.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Memiliki 4 sumbu simetri lipat.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Sudut-sudut yang berhadapan sama besar.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -953,7 +998,11 @@
       <c r="H13" t="n">
         <v>60</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -963,27 +1012,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Matematika 13: contoh soal numerasi sederhana.</t>
+          <t>Sebuah bangun datar gabungan tersusun dari sebuah persegi panjang berukuran panjang 20 cm dan lebar 10 cm, serta sebuah segitiga siku-siku dengan panjang alas 15 cm dan tinggi 10 cm yang menempel pada salah satu sisi lebarnya. Luas total bangun tersebut adalah....</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  250 cm²</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  275 cm²</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  300 cm²</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  325 cm²</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -994,7 +1043,11 @@
       <c r="H14" t="n">
         <v>60</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1004,27 +1057,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Matematika 14: contoh soal numerasi sederhana.</t>
+          <t>Sebuah drum minyak berbentuk tabung memiliki jari-jari alas 35 cm dan tinggi 100 cm. (Gunakan π = 22/7). Berapakah volume minyak yang dapat ditampung drum tersebut jika diisi sampai penuh? (1 liter = 1.000 cm³)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  385 liter</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  420 liter</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  450 liter</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  770 liter</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1035,17 +1088,21 @@
       <c r="H15" t="n">
         <v>60</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Matematika 15: contoh soal numerasi sederhana.</t>
+          <t>Tentukan kebenaran dari pernyataan mengenai karakteristik bangun ruang prisma segitiga dan balok berikut!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1076,7 +1133,11 @@
       <c r="H16" t="n">
         <v>60</v>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1086,27 +1147,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Matematika 16: contoh soal numerasi sederhana.</t>
+          <t>Nilai ulangan IPA Wulan pada lima kali penilaian adalah: 80, 85, 75, 90, dan 85. Jika Wulan menginginkan nilai rata-rata dari enam kali ulangan menjadi 84, berapakah nilai yang harus diraih Wulan pada ulangan keenam?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  88</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  89</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  90</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  92</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1117,7 +1178,11 @@
       <c r="H17" t="n">
         <v>60</v>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1127,27 +1192,33 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Matematika 17: contoh soal numerasi sederhana.</t>
+          <t>Data ukuran sepatu siswa kelas 6 disajikan dalam tabel:
+• Ukuran 36: 4 siswa
+• Ukuran 37: 8 siswa
+• Ukuran 38: 12 siswa
+• Ukuran 39: 10 siswa
+• Ukuran 40: 6 siswa
+Modus ukuran sepatu siswa kelas 6 tersebut adalah....</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Ukuran 37</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Ukuran 38</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Ukuran 39</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Ukuran 40</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1158,37 +1229,45 @@
       <c r="H18" t="n">
         <v>60</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Matematika 18: contoh soal numerasi sederhana.</t>
+          <t>Perhatikan data perolehan medali SD Nusantara pada lomba antarsekolah:
+• Emas: 12 medali
+• Perak: 16 medali
+• Perunggu: 20 medali
+Manakah pernyataan analisis berikut yang BENAR?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Total seluruh medali yang diraih adalah 48 medali.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Perbandingan banyak medali emas dan perak adalah 3 : 4.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Medali perunggu menyumbang lebih dari 50% dari total perolehan medali.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Selisih banyak medali perunggu dan emas adalah 8 medali.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1199,7 +1278,11 @@
       <c r="H19" t="n">
         <v>60</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1209,27 +1292,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Matematika 19: contoh soal numerasi sederhana.</t>
+          <t>Sebuah diagram lingkaran (360°) menggambarkan jenis tanaman buah di kebun Pak Joko yang berjumlah total 180 pohon. Sudut juring untuk pohon mangga adalah 120°, pohon jeruk 90°, pohon durian 70°, dan sisanya pohon rambutan. Banyak pohon rambutan di kebun tersebut adalah....</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  35 pohon</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  40 pohon</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  45 pohon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  50 pohon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1240,17 +1323,21 @@
       <c r="H20" t="n">
         <v>60</v>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Matematika 20: contoh soal numerasi sederhana.</t>
+          <t>Di dalam gedung bioskop mini, barisan kursi diatur teratur. Baris paling depan (baris 1) berisi 10 kursi, baris kedua berisi 14 kursi, baris ketiga berisi 18 kursi, dan seterusnya bertambah tetap. Tentukan kebenaran dari pernyataan berikut!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1281,7 +1368,11 @@
       <c r="H21" t="n">
         <v>60</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
